--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8132,6 +8132,220 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122907435</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skärlötamarken, Ög</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>563031</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6504257</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122907434</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skärlötamarken, Ög</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>563040</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6504252</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8137,7 +8137,7 @@
         <v>122907435</v>
       </c>
       <c r="B69" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>122907434</v>
       </c>
       <c r="B70" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8134,10 +8134,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122907435</v>
+        <v>122907434</v>
       </c>
       <c r="B69" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>33</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563031</v>
+        <v>563040</v>
       </c>
       <c r="R69" t="n">
-        <v>6504257</v>
+        <v>6504252</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8241,10 +8241,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122907434</v>
+        <v>122907435</v>
       </c>
       <c r="B70" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563040</v>
+        <v>563031</v>
       </c>
       <c r="R70" t="n">
-        <v>6504252</v>
+        <v>6504257</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8134,10 +8134,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122907434</v>
+        <v>122907435</v>
       </c>
       <c r="B69" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563040</v>
+        <v>563031</v>
       </c>
       <c r="R69" t="n">
-        <v>6504252</v>
+        <v>6504257</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8241,10 +8241,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122907435</v>
+        <v>122907434</v>
       </c>
       <c r="B70" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>33</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563031</v>
+        <v>563040</v>
       </c>
       <c r="R70" t="n">
-        <v>6504257</v>
+        <v>6504252</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8137,7 +8137,7 @@
         <v>122907435</v>
       </c>
       <c r="B69" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>122907434</v>
       </c>
       <c r="B70" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8137,7 +8137,7 @@
         <v>122907435</v>
       </c>
       <c r="B69" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>122907434</v>
       </c>
       <c r="B70" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4829,10 +4829,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113349418</v>
+        <v>119221173</v>
       </c>
       <c r="B37" t="n">
-        <v>97650</v>
+        <v>94679</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4841,45 +4841,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Bengölen, Ög</t>
+          <t>Väster om Stora Bengölen, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563032</v>
+        <v>562821</v>
       </c>
       <c r="R37" t="n">
-        <v>6504239</v>
+        <v>6504492</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4901,19 +4897,14 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>E-Nor-0738</t>
-        </is>
-      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4928,26 +4919,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Marika Sjödin, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113349413</v>
+        <v>119221125</v>
       </c>
       <c r="B38" t="n">
-        <v>97650</v>
+        <v>90560</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4956,55 +4943,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>L. Bergsätter VNV 616 m, Ög</t>
+          <t>Väster om Stora Bengölen, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563027</v>
+        <v>562802</v>
       </c>
       <c r="R38" t="n">
-        <v>6504268</v>
+        <v>6504459</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5026,19 +4999,14 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>E-Nor-0742</t>
-        </is>
-      </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5049,35 +5017,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Marika Sjödin, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119221173</v>
+        <v>119221155</v>
       </c>
       <c r="B39" t="n">
-        <v>94679</v>
+        <v>91838</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5090,21 +5049,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5114,10 +5073,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562821</v>
+        <v>562766</v>
       </c>
       <c r="R39" t="n">
-        <v>6504492</v>
+        <v>6504458</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5176,7 +5135,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119221125</v>
+        <v>119221126</v>
       </c>
       <c r="B40" t="n">
         <v>90560</v>
@@ -5216,10 +5175,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562802</v>
+        <v>562843</v>
       </c>
       <c r="R40" t="n">
-        <v>6504459</v>
+        <v>6504442</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5278,10 +5237,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119221155</v>
+        <v>119221179</v>
       </c>
       <c r="B41" t="n">
-        <v>91838</v>
+        <v>91183</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5294,21 +5253,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5318,10 +5277,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562766</v>
+        <v>562789</v>
       </c>
       <c r="R41" t="n">
-        <v>6504458</v>
+        <v>6504443</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5380,10 +5339,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119221126</v>
+        <v>119221147</v>
       </c>
       <c r="B42" t="n">
-        <v>90560</v>
+        <v>90964</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5392,25 +5351,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5420,10 +5379,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562843</v>
+        <v>562775</v>
       </c>
       <c r="R42" t="n">
-        <v>6504442</v>
+        <v>6504524</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5482,10 +5441,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119221179</v>
+        <v>119221129</v>
       </c>
       <c r="B43" t="n">
-        <v>91183</v>
+        <v>91882</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5494,25 +5453,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6031</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5522,10 +5481,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562789</v>
+        <v>562679</v>
       </c>
       <c r="R43" t="n">
-        <v>6504443</v>
+        <v>6504575</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5584,10 +5543,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119221147</v>
+        <v>119221170</v>
       </c>
       <c r="B44" t="n">
-        <v>90964</v>
+        <v>91838</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5600,21 +5559,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5624,10 +5583,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562775</v>
+        <v>562784</v>
       </c>
       <c r="R44" t="n">
-        <v>6504524</v>
+        <v>6504453</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5686,10 +5645,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119221129</v>
+        <v>119221154</v>
       </c>
       <c r="B45" t="n">
-        <v>91882</v>
+        <v>91838</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5698,25 +5657,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5726,10 +5685,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562679</v>
+        <v>562755</v>
       </c>
       <c r="R45" t="n">
-        <v>6504575</v>
+        <v>6504465</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5788,10 +5747,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119221170</v>
+        <v>119221130</v>
       </c>
       <c r="B46" t="n">
-        <v>91838</v>
+        <v>94429</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5804,21 +5763,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>2818</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5828,10 +5787,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562784</v>
+        <v>562785</v>
       </c>
       <c r="R46" t="n">
-        <v>6504453</v>
+        <v>6504486</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5890,10 +5849,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119221154</v>
+        <v>119221178</v>
       </c>
       <c r="B47" t="n">
-        <v>91838</v>
+        <v>94679</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5906,21 +5865,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5930,10 +5889,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562755</v>
+        <v>562809</v>
       </c>
       <c r="R47" t="n">
-        <v>6504465</v>
+        <v>6504515</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5992,10 +5951,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119221130</v>
+        <v>119221128</v>
       </c>
       <c r="B48" t="n">
-        <v>94429</v>
+        <v>91848</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6004,25 +5963,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>789</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6032,10 +5991,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562785</v>
+        <v>562841</v>
       </c>
       <c r="R48" t="n">
-        <v>6504486</v>
+        <v>6504457</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6094,10 +6053,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119221178</v>
+        <v>119221160</v>
       </c>
       <c r="B49" t="n">
-        <v>94679</v>
+        <v>91838</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6110,21 +6069,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6134,10 +6093,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562809</v>
+        <v>562792</v>
       </c>
       <c r="R49" t="n">
-        <v>6504515</v>
+        <v>6504471</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6196,10 +6155,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119221128</v>
+        <v>119221149</v>
       </c>
       <c r="B50" t="n">
-        <v>91848</v>
+        <v>90964</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6208,25 +6167,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>789</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6236,10 +6195,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562841</v>
+        <v>562787</v>
       </c>
       <c r="R50" t="n">
-        <v>6504457</v>
+        <v>6504511</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6298,10 +6257,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119221160</v>
+        <v>119221146</v>
       </c>
       <c r="B51" t="n">
-        <v>91838</v>
+        <v>105002</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6314,21 +6273,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6338,10 +6297,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562792</v>
+        <v>562793</v>
       </c>
       <c r="R51" t="n">
-        <v>6504471</v>
+        <v>6504514</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6400,10 +6359,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119221149</v>
+        <v>119221136</v>
       </c>
       <c r="B52" t="n">
-        <v>90964</v>
+        <v>8430</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6416,21 +6375,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6440,10 +6399,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562787</v>
+        <v>562788</v>
       </c>
       <c r="R52" t="n">
-        <v>6504511</v>
+        <v>6504488</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6502,10 +6461,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119221146</v>
+        <v>119221145</v>
       </c>
       <c r="B53" t="n">
-        <v>105002</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6514,25 +6473,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>788</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6542,10 +6501,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562793</v>
+        <v>562760</v>
       </c>
       <c r="R53" t="n">
-        <v>6504514</v>
+        <v>6504531</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6604,10 +6563,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119221136</v>
+        <v>119221161</v>
       </c>
       <c r="B54" t="n">
-        <v>8430</v>
+        <v>91838</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6620,21 +6579,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6644,10 +6603,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562788</v>
+        <v>562844</v>
       </c>
       <c r="R54" t="n">
-        <v>6504488</v>
+        <v>6504448</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6706,10 +6665,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119221145</v>
+        <v>119221157</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91838</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6718,25 +6677,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>788</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6746,10 +6705,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562760</v>
+        <v>562766</v>
       </c>
       <c r="R55" t="n">
-        <v>6504531</v>
+        <v>6504494</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6808,10 +6767,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119221161</v>
+        <v>119221152</v>
       </c>
       <c r="B56" t="n">
-        <v>91838</v>
+        <v>90964</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6824,21 +6783,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6848,10 +6807,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562844</v>
+        <v>562836</v>
       </c>
       <c r="R56" t="n">
-        <v>6504448</v>
+        <v>6504530</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6910,10 +6869,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119221157</v>
+        <v>119221151</v>
       </c>
       <c r="B57" t="n">
-        <v>91838</v>
+        <v>90964</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6926,21 +6885,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6950,10 +6909,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562766</v>
+        <v>562832</v>
       </c>
       <c r="R57" t="n">
-        <v>6504494</v>
+        <v>6504525</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7012,10 +6971,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119221152</v>
+        <v>119221162</v>
       </c>
       <c r="B58" t="n">
-        <v>90964</v>
+        <v>91838</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7028,21 +6987,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7052,10 +7011,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562836</v>
+        <v>562788</v>
       </c>
       <c r="R58" t="n">
-        <v>6504530</v>
+        <v>6504525</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7114,7 +7073,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119221151</v>
+        <v>119221153</v>
       </c>
       <c r="B59" t="n">
         <v>90964</v>
@@ -7154,10 +7113,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562832</v>
+        <v>562761</v>
       </c>
       <c r="R59" t="n">
-        <v>6504525</v>
+        <v>6504446</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7216,10 +7175,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119221162</v>
+        <v>120779184</v>
       </c>
       <c r="B60" t="n">
-        <v>91838</v>
+        <v>94844</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7232,34 +7191,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster om Stora Bengölen, Ög</t>
+          <t>Skärlötamarken, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562788</v>
+        <v>563029</v>
       </c>
       <c r="R60" t="n">
-        <v>6504525</v>
+        <v>6504224</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7286,12 +7245,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7311,17 +7270,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Suvi Sivula</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119221153</v>
+        <v>120779138</v>
       </c>
       <c r="B61" t="n">
-        <v>90964</v>
+        <v>8432</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7334,34 +7293,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster om Stora Bengölen, Ög</t>
+          <t>Skärlötamarken, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562761</v>
+        <v>562671</v>
       </c>
       <c r="R61" t="n">
-        <v>6504446</v>
+        <v>6504589</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7388,12 +7347,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7413,17 +7372,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Suvi Sivula</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120779184</v>
+        <v>120779170</v>
       </c>
       <c r="B62" t="n">
-        <v>94844</v>
+        <v>91963</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7436,21 +7395,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7460,10 +7419,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>563029</v>
+        <v>562720</v>
       </c>
       <c r="R62" t="n">
-        <v>6504224</v>
+        <v>6504434</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7522,10 +7481,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120779138</v>
+        <v>120779168</v>
       </c>
       <c r="B63" t="n">
-        <v>8432</v>
+        <v>91963</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7538,21 +7497,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7562,10 +7521,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562671</v>
+        <v>562836</v>
       </c>
       <c r="R63" t="n">
-        <v>6504589</v>
+        <v>6504510</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7624,7 +7583,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120779170</v>
+        <v>120779169</v>
       </c>
       <c r="B64" t="n">
         <v>91963</v>
@@ -7664,10 +7623,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562720</v>
+        <v>562704</v>
       </c>
       <c r="R64" t="n">
-        <v>6504434</v>
+        <v>6504603</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7726,10 +7685,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120779168</v>
+        <v>120779139</v>
       </c>
       <c r="B65" t="n">
-        <v>91963</v>
+        <v>8432</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7742,21 +7701,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7766,10 +7725,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562836</v>
+        <v>562694</v>
       </c>
       <c r="R65" t="n">
-        <v>6504510</v>
+        <v>6504620</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7828,10 +7787,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120779169</v>
+        <v>120779124</v>
       </c>
       <c r="B66" t="n">
-        <v>91963</v>
+        <v>90707</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7840,25 +7799,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7868,10 +7827,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562704</v>
+        <v>562696</v>
       </c>
       <c r="R66" t="n">
-        <v>6504603</v>
+        <v>6504606</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7930,10 +7889,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120779139</v>
+        <v>122907435</v>
       </c>
       <c r="B67" t="n">
-        <v>8432</v>
+        <v>98396</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7942,38 +7901,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärlötamarken, Ög</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562694</v>
+        <v>563031</v>
       </c>
       <c r="R67" t="n">
-        <v>6504620</v>
+        <v>6504257</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8000,12 +7963,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8014,6 +7977,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8032,10 +7996,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120779124</v>
+        <v>122907434</v>
       </c>
       <c r="B68" t="n">
-        <v>90707</v>
+        <v>98396</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8044,38 +8008,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skärlötamarken, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562696</v>
+        <v>563040</v>
       </c>
       <c r="R68" t="n">
-        <v>6504606</v>
+        <v>6504252</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8102,12 +8070,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,6 +8084,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8131,220 +8100,6 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>122907435</v>
-      </c>
-      <c r="B69" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Skärlötamarken, Ög</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>563031</v>
-      </c>
-      <c r="R69" t="n">
-        <v>6504257</v>
-      </c>
-      <c r="S69" t="n">
-        <v>15</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Kvillinge</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>122907434</v>
-      </c>
-      <c r="B70" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Skärlötamarken, Ög</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>563040</v>
-      </c>
-      <c r="R70" t="n">
-        <v>6504252</v>
-      </c>
-      <c r="S70" t="n">
-        <v>15</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Kvillinge</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8101,6 +8101,232 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125595671</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58459</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Väster om Stora Bengölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>562912</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6504205</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125595587</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92135</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4786</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mandelriska</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lactifluus volemus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Väster om Stora Bengölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>562912</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6504205</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8327,6 +8327,132 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125635104</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91186</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Väster om Stora Bengölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>562734</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6504559</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8453,6 +8453,130 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125673041</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58459</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Väster om Stora Bengölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>562906</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6504335</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8106,12 +8106,7 @@
         <v>125595671</v>
       </c>
       <c r="B69" t="n">
-        <v>58459</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58479</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8226,12 +8221,7 @@
         <v>125595587</v>
       </c>
       <c r="B70" t="n">
-        <v>92135</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92188</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8253,7 +8243,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Kuntze</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8332,12 +8322,7 @@
         <v>125635104</v>
       </c>
       <c r="B71" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8458,12 +8443,7 @@
         <v>125673041</v>
       </c>
       <c r="B72" t="n">
-        <v>58459</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58479</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8221,7 +8221,7 @@
         <v>125595587</v>
       </c>
       <c r="B70" t="n">
-        <v>92188</v>
+        <v>92195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>125635104</v>
       </c>
       <c r="B71" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8106,7 +8106,7 @@
         <v>125595671</v>
       </c>
       <c r="B69" t="n">
-        <v>58479</v>
+        <v>58480</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>125595587</v>
       </c>
       <c r="B70" t="n">
-        <v>92195</v>
+        <v>92199</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>125635104</v>
       </c>
       <c r="B71" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>125673041</v>
       </c>
       <c r="B72" t="n">
-        <v>58479</v>
+        <v>58480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8221,7 +8221,7 @@
         <v>125595587</v>
       </c>
       <c r="B70" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>125635104</v>
       </c>
       <c r="B71" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8557,6 +8557,200 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126163076</v>
+      </c>
+      <c r="B73" t="n">
+        <v>95692</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skärlötamarken, Ög</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>563035</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6504237</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126163077</v>
+      </c>
+      <c r="B74" t="n">
+        <v>95788</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>210</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skärlötamarken, Ög</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>563040</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6504248</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8106,7 +8106,7 @@
         <v>125595671</v>
       </c>
       <c r="B69" t="n">
-        <v>58480</v>
+        <v>58481</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>125595587</v>
       </c>
       <c r="B70" t="n">
-        <v>92203</v>
+        <v>92205</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>125635104</v>
       </c>
       <c r="B71" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>125673041</v>
       </c>
       <c r="B72" t="n">
-        <v>58480</v>
+        <v>58481</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>126163076</v>
       </c>
       <c r="B73" t="n">
-        <v>95692</v>
+        <v>95694</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>126163077</v>
       </c>
       <c r="B74" t="n">
-        <v>95788</v>
+        <v>95790</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8221,7 +8221,7 @@
         <v>125595587</v>
       </c>
       <c r="B70" t="n">
-        <v>92205</v>
+        <v>92207</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>125635104</v>
       </c>
       <c r="B71" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>126163076</v>
       </c>
       <c r="B73" t="n">
-        <v>95694</v>
+        <v>95696</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>126163077</v>
       </c>
       <c r="B74" t="n">
-        <v>95790</v>
+        <v>95792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8221,7 +8221,7 @@
         <v>125595587</v>
       </c>
       <c r="B70" t="n">
-        <v>92207</v>
+        <v>92209</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>125635104</v>
       </c>
       <c r="B71" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>126163076</v>
       </c>
       <c r="B73" t="n">
-        <v>95696</v>
+        <v>95698</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>126163077</v>
       </c>
       <c r="B74" t="n">
-        <v>95792</v>
+        <v>95794</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8322,7 +8322,7 @@
         <v>125635104</v>
       </c>
       <c r="B71" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>125673041</v>
       </c>
       <c r="B72" t="n">
-        <v>58481</v>
+        <v>58485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>126163076</v>
       </c>
       <c r="B73" t="n">
-        <v>95698</v>
+        <v>95702</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>126163077</v>
       </c>
       <c r="B74" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8562,7 +8562,7 @@
         <v>126163076</v>
       </c>
       <c r="B73" t="n">
-        <v>95702</v>
+        <v>95705</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>126163077</v>
       </c>
       <c r="B74" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -8562,7 +8562,7 @@
         <v>126163076</v>
       </c>
       <c r="B73" t="n">
-        <v>95705</v>
+        <v>95714</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>126163077</v>
       </c>
       <c r="B74" t="n">
-        <v>95801</v>
+        <v>95810</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -6362,12 +6362,7 @@
         <v>119221136</v>
       </c>
       <c r="B52" t="n">
-        <v>8430</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6393,6 +6388,15 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väster om Stora Bengölen, Ög</t>
@@ -7280,12 +7284,7 @@
         <v>120779138</v>
       </c>
       <c r="B61" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7311,6 +7310,15 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärlötamarken, Ög</t>
@@ -7361,6 +7369,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7688,12 +7697,7 @@
         <v>120779139</v>
       </c>
       <c r="B65" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7719,6 +7723,15 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärlötamarken, Ög</t>
@@ -7769,6 +7782,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14506-2023 artfynd.xlsx
+++ b/artfynd/A 14506-2023 artfynd.xlsx
@@ -6362,7 +6362,7 @@
         <v>119221136</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>120779138</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>120779139</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
